--- a/satisfaction_surveys/001_microfinance_awareness_survey--satisfaction_surveys.xlsx
+++ b/satisfaction_surveys/001_microfinance_awareness_survey--satisfaction_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'very_well',_'label':_'very_well'}</t>
+          <t>very_well</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Very well', 'label': 'Very well'}</t>
+          <t>Very well</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'not_very_well',_'label':_'not_very_well'}</t>
+          <t>not_very_well</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Not very well', 'label': 'Not very well'}</t>
+          <t>Not very well</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'not_at_all',_'label':_'not_at_all'}</t>
+          <t>not_at_all</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Not at all', 'label': 'Not at all'}</t>
+          <t>Not at all</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'radio/tv',_'label':_'radio/tv'}</t>
+          <t>radio/tv</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Radio/TV', 'label': 'Radio/TV'}</t>
+          <t>Radio/TV</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'internet',_'label':_'internet'}</t>
+          <t>internet</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Internet', 'label': 'Internet'}</t>
+          <t>Internet</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'newspapers',_'label':_'newspapers'}</t>
+          <t>newspapers</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Newspapers', 'label': 'Newspapers'}</t>
+          <t>Newspapers</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'social_media',_'label':_'social_media'}</t>
+          <t>social_media</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Social media', 'label': 'Social media'}</t>
+          <t>Social media</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'word_of_mouth',_'label':_'word_of_mouth'}</t>
+          <t>word_of_mouth</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Word of mouth', 'label': 'Word of mouth'}</t>
+          <t>Word of mouth</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'other',_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Other', 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_"don't_know",_'label':_"don't_know"}</t>
+          <t>don't_know</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': "Don't know", 'label': "Don't know"}</t>
+          <t>Don't know</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'very_interested',_'label':_'very_interested'}</t>
+          <t>very_interested</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Very interested', 'label': 'Very interested'}</t>
+          <t>Very interested</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'somewhat_interested',_'label':_'somewhat_interested'}</t>
+          <t>somewhat_interested</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Somewhat interested', 'label': 'Somewhat interested'}</t>
+          <t>Somewhat interested</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'not_very_interested',_'label':_'not_very_interested'}</t>
+          <t>not_very_interested</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Not very interested', 'label': 'Not very interested'}</t>
+          <t>Not very interested</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'not_at_all_interested',_'label':_'not_at_all_interested'}</t>
+          <t>not_at_all_interested</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Not at all interested', 'label': 'Not at all interested'}</t>
+          <t>Not at all interested</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'mfa',_'label':_'mfa'}</t>
+          <t>mfa</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'MfA', 'label': 'MfA'}</t>
+          <t>MfA</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'mfs',_'label':_'mfs'}</t>
+          <t>mfs</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'MfS', 'label': 'MfS'}</t>
+          <t>MfS</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'other',_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'Other', 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'none',_'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'None', 'label': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'mfs',_'label':_'mfs'}</t>
+          <t>mfs</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'MFS', 'label': 'MFS'}</t>
+          <t>MFS</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_'mfb',_'label':_'mfb'}</t>
+          <t>mfb</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 'MFB', 'label': 'MFB'}</t>
+          <t>MFB</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_'other',_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 'Other', 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_'none',_'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': 'None', 'label': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_'positive',_'label':_'positive'}</t>
+          <t>positive</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': 'Positive', 'label': 'Positive'}</t>
+          <t>Positive</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'value':_'negative',_'label':_'negative'}</t>
+          <t>negative</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'value': 'Negative', 'label': 'Negative'}</t>
+          <t>Negative</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'value':_'neutral',_'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'value': 'Neutral', 'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'value':_true,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'value': True, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'value':_false,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'value': False, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'value':_'male',_'label':_'male'}</t>
+          <t>male</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'value': 'Male', 'label': 'Male'}</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'value':_'female',_'label':_'female'}</t>
+          <t>female</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'value': 'Female', 'label': 'Female'}</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'value':_'prefer_not_to_say',_'label':_'prefer_not_to_say'}</t>
+          <t>prefer_not_to_say</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'value': 'Prefer not to say', 'label': 'Prefer not to say'}</t>
+          <t>Prefer not to say</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'value':_'primary',_'label':_'primary'}</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'value': 'Primary', 'label': 'Primary'}</t>
+          <t>Primary</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'value':_'secondary',_'label':_'secondary'}</t>
+          <t>secondary</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'value': 'Secondary', 'label': 'Secondary'}</t>
+          <t>Secondary</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'value':_'high_school',_'label':_'high_school'}</t>
+          <t>high_school</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'value': 'High school', 'label': 'High school'}</t>
+          <t>High school</t>
         </is>
       </c>
     </row>
@@ -1692,12 +1692,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'value':_'university',_'label':_'university'}</t>
+          <t>university</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'value': 'University', 'label': 'University'}</t>
+          <t>University</t>
         </is>
       </c>
     </row>
@@ -1709,12 +1709,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'value':_'tertiary',_'label':_'tertiary'}</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'value': 'Tertiary', 'label': 'Tertiary'}</t>
+          <t>Tertiary</t>
         </is>
       </c>
     </row>
@@ -1726,12 +1726,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'value':_'other',_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'value': 'Other', 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1743,12 +1743,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'value':_'less_than_5_years',_'label':_'less_than_5_years'}</t>
+          <t>less_than_5_years</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'value': 'Less than 5 years', 'label': 'Less than 5 years'}</t>
+          <t>Less than 5 years</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'value':_'5-10_years',_'label':_'5-10_years'}</t>
+          <t>5-10_years</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'value': '5-10 years', 'label': '5-10 years'}</t>
+          <t>5-10 years</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'value':_'more_than_10_years',_'label':_'more_than_10_years'}</t>
+          <t>more_than_10_years</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'value': 'More than 10 years', 'label': 'More than 10 years'}</t>
+          <t>More than 10 years</t>
         </is>
       </c>
     </row>
@@ -1794,12 +1794,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'value':_'radio/tv',_'label':_'radio/tv'}</t>
+          <t>radio/tv</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'value': 'Radio/TV', 'label': 'Radio/TV'}</t>
+          <t>Radio/TV</t>
         </is>
       </c>
     </row>
@@ -1811,12 +1811,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'value':_'internet',_'label':_'internet'}</t>
+          <t>internet</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'value': 'Internet', 'label': 'Internet'}</t>
+          <t>Internet</t>
         </is>
       </c>
     </row>
@@ -1828,12 +1828,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'value':_'newspapers',_'label':_'newspapers'}</t>
+          <t>newspapers</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'value': 'Newspapers', 'label': 'Newspapers'}</t>
+          <t>Newspapers</t>
         </is>
       </c>
     </row>
@@ -1845,12 +1845,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'value':_'social_media',_'label':_'social_media'}</t>
+          <t>social_media</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'value': 'Social media', 'label': 'Social media'}</t>
+          <t>Social media</t>
         </is>
       </c>
     </row>
@@ -1862,12 +1862,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'value':_'word_of_mouth',_'label':_'word_of_mouth'}</t>
+          <t>word_of_mouth</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'value': 'Word of mouth', 'label': 'Word of mouth'}</t>
+          <t>Word of mouth</t>
         </is>
       </c>
     </row>
@@ -1879,12 +1879,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'value':_'other',_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'value': 'Other', 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1896,12 +1896,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'value':_"don't_know",_'label':_"don't_know"}</t>
+          <t>don't_know</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'value': "Don't know", 'label': "Don't know"}</t>
+          <t>Don't know</t>
         </is>
       </c>
     </row>
@@ -1913,12 +1913,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'value':_'very_aware',_'label':_'very_aware'}</t>
+          <t>very_aware</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'value': 'Very aware', 'label': 'Very aware'}</t>
+          <t>Very aware</t>
         </is>
       </c>
     </row>
@@ -1930,12 +1930,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{'value':_'somewhat_aware',_'label':_'somewhat_aware'}</t>
+          <t>somewhat_aware</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{'value': 'Somewhat aware', 'label': 'Somewhat aware'}</t>
+          <t>Somewhat aware</t>
         </is>
       </c>
     </row>
@@ -1947,12 +1947,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{'value':_'not_very_aware',_'label':_'not_very_aware'}</t>
+          <t>not_very_aware</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{'value': 'Not very aware', 'label': 'Not very aware'}</t>
+          <t>Not very aware</t>
         </is>
       </c>
     </row>
@@ -1964,12 +1964,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>{'value':_'not_at_all_aware',_'label':_'not_at_all_aware'}</t>
+          <t>not_at_all_aware</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{'value': 'Not at all aware', 'label': 'Not at all aware'}</t>
+          <t>Not at all aware</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>{'value':_true,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>{'value': True, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1998,12 +1998,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>{'value':_false,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>{'value': False, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
